--- a/public/decks/Travidz_Financial_Model_v2_Global.xlsx
+++ b/public/decks/Travidz_Financial_Model_v2_Global.xlsx
@@ -2259,7 +2259,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="43" t="inlineStr">
         <is>
@@ -2569,7 +2568,6 @@
         <v/>
       </c>
     </row>
-    <row r="16"/>
     <row r="17">
       <c r="A17" s="43" t="inlineStr">
         <is>
@@ -2698,8 +2696,6 @@
         <v/>
       </c>
     </row>
-    <row r="29"/>
-    <row r="30"/>
     <row r="31">
       <c r="A31" s="43" t="inlineStr">
         <is>
@@ -2801,8 +2797,6 @@
         <v/>
       </c>
     </row>
-    <row r="37"/>
-    <row r="38"/>
     <row r="39">
       <c r="A39" s="46" t="inlineStr">
         <is>
@@ -2859,7 +2853,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="49" t="inlineStr">
         <is>
@@ -3054,8 +3047,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="55" t="inlineStr">
         <is>
@@ -3198,7 +3189,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="49" t="inlineStr">
         <is>
@@ -6228,7 +6218,7 @@
         </is>
       </c>
       <c r="B123" s="15" t="n">
-        <v>2000000</v>
+        <v>2500000</v>
       </c>
       <c r="C123" s="15" t="n">
         <v>1500000</v>
@@ -6387,7 +6377,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="46" t="inlineStr">
         <is>
@@ -6395,7 +6384,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="43" t="inlineStr">
         <is>
@@ -6665,8 +6653,6 @@
         <v/>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="43" t="inlineStr">
         <is>
@@ -6898,7 +6884,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="21" t="inlineStr">
         <is>
@@ -17449,7 +17434,6 @@
         <v/>
       </c>
     </row>
-    <row r="43"/>
     <row r="44">
       <c r="A44" s="29" t="n"/>
       <c r="B44" s="27" t="inlineStr">
@@ -19962,7 +19946,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="37" t="inlineStr">
         <is>
@@ -21018,7 +21001,6 @@
         <v/>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="34" t="inlineStr">
         <is>
@@ -21767,7 +21749,6 @@
         <v/>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="34" t="inlineStr">
         <is>
@@ -24245,8 +24226,6 @@
         <v/>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26"/>
     <row r="27">
       <c r="A27" s="34" t="inlineStr">
         <is>
@@ -24477,7 +24456,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="37" t="inlineStr">
         <is>
@@ -25802,7 +25780,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="37" t="inlineStr">
         <is>
@@ -28587,7 +28564,6 @@
         <v/>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="34" t="inlineStr">
         <is>
@@ -31559,7 +31535,6 @@
         <v/>
       </c>
     </row>
-    <row r="29"/>
     <row r="30">
       <c r="A30" s="34" t="inlineStr">
         <is>
@@ -32308,7 +32283,6 @@
         <v/>
       </c>
     </row>
-    <row r="34"/>
     <row r="35">
       <c r="A35" s="34" t="inlineStr">
         <is>
